--- a/tc15.xlsx
+++ b/tc15.xlsx
@@ -425,87 +425,201 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>user_story_id</t>
+          <t>Name Precondition Test Step Expected Result Test Case Attachment</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>Id Test Step #</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Attachments Test Step Description</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>priority</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Test Case Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>US-001</t>
+          <t>Verify Valid EDI 270 Inquiry File Generation for Delinquency Status</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Generate EDI 270 Inquiry File</t>
+          <t>TC-EDI270-271-DEL-001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>As a user, I want to generate a valid EDI 270 inquiry file so that eligibility requests can be processed successfully.</t>
+          <t>sample_edi270_valid_01.txt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>Draft</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>US-002</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Validate EDI 271 Response</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>As a user, I want to validate the EDI 271 response file so that delinquency status details are correctly received.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+          <t>Generate a valid EDI 270 eligibility inquiry file with correct ISA/GS headers, 2000C subscriber loop with patient details, and ensure the file is properly formatted for the four trading partners. Verify all mandatory segments (ISA, GS, ST, BHT, HL, NM1, DMG, DTP) are present and data elements comply with the specification.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>System configured with trading partner IDs for Availity, ETSPassport, Dorado, Instamed. Valid subscriber data available. sample_input_270.json</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Prepare valid subscriber and provider input data including member ID, name, DOB, gender, and trading partner ID.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Input data is prepared with correct formats and trading partner identifiers.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>generated_270_01.txt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Generate the 270 file using the prepared input data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>270_schema_validation_report.json</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Validate the generated 270 file against the ANSI X12 270 schema and implementation guide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Verify 271 Response File Includes Delinquency Status EB01=5 (Active - Pending Investigation)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TC-EDI270-271-DEL-002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sample_edi271_valid_01.txt</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>Draft</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Valid 270 inquiry submitted for member with delinquency status active within 0-30 days. generated_271_01.txt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Receive the 271 response file corresponding to the 270 inquiry.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>271 file is received containing loop 2110C with EB segment having EB01 = "5".</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>271_schema_validation_report.json</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Validate the 271 file against the ANSI X12 271 schema and implementation guide.</t>
         </is>
       </c>
     </row>
